--- a/sampleprojects/TaxReturn/excel/states/NY.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/NY.xlsx
@@ -83,7 +83,7 @@
     <t>MFJ/QSS: $16,050 std ded, 10.9%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.agi - 16050.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.109</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 16050.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.109</t>
   </si>
   <si>
     <t>X</t>
@@ -92,13 +92,13 @@
     <t>HOH: $11,200 std ded, 10.9%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.agi - 11200.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.109</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 11200.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.109</t>
   </si>
   <si>
     <t>Default (Single/MFS): $8,000 std ded, 10.9%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.agi - 8000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.109</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 8000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.109</t>
   </si>
   <si>
     <t>Policy:</t>

--- a/sampleprojects/TaxReturn/excel/states/NY.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/NY.xlsx
@@ -44,7 +44,7 @@
     <t/>
   </si>
   <si>
-    <t>set result.computed_state_tax = 0; set result.computed_state_taxable_income = 0; add "  New York Tax Calculation (top marginal 10.9%)" to job.audit_trail</t>
+    <t>set result.computed_state_tax = 0; set result.computed_state_taxable_income = 0; add "  New York Tax Calculation (top marginal 10.9%)" to job.audit_trail; set result.ny_military_retirement_exclusion = result.military_retirement_income; add "  NY IT-201 line 26 federal (military) pension subtraction: $" + result.ny_military_retirement_exclusion to job.audit_trail</t>
   </si>
   <si>
     <t>CONDITIONS: COMMENTS</t>
@@ -83,7 +83,7 @@
     <t>MFJ/QSS: $16,050 std ded, 10.9%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 16050.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.109</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.ny_military_retirement_exclusion - 16050.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.109</t>
   </si>
   <si>
     <t>X</t>
@@ -92,13 +92,13 @@
     <t>HOH: $11,200 std ded, 10.9%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 11200.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.109</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.ny_military_retirement_exclusion - 11200.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.109</t>
   </si>
   <si>
     <t>Default (Single/MFS): $8,000 std ded, 10.9%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 8000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.109</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.ny_military_retirement_exclusion - 8000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.109</t>
   </si>
   <si>
     <t>Policy:</t>
@@ -395,7 +395,7 @@
     <t>0.0</t>
   </si>
   <si>
-    <t>NY military retirement exclusion (computed - 100% exempt). New York Tax Law §612(c)(30). IT-201 Line 28 subtraction. New York provides full exclusion for US military retirement pay and SBP payments. No AGI limits. No age restrictions. One of most generous state military tax benefits. MOAA State Report Card 2025: Grade A. Honors MSRRA (spouse income exempt if different domicile) and SCRA (active duty pay exempt if different state of residence). Source: NYS Tax Department, MOAA</t>
+    <t>NY subtraction of military retired pay (computed per return in NY_Tax): pensions of the federal government, including the military, are subtracted in full on IT-201 line 26 (Tax Law 612(c)(3)(ii); 2025 IT-201-I p. 9). No age limit or cap; the $20,000 line 29 exclusion is for other pensions at 59 1/2 (#1330).</t>
   </si>
   <si>
     <t>ny_standard_deduction_hoh</t>

--- a/sampleprojects/TaxReturn/excel/states/NY.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/NY.xlsx
@@ -44,7 +44,7 @@
     <t/>
   </si>
   <si>
-    <t>set result.computed_state_tax = 0; set result.computed_state_taxable_income = 0; add "  New York Tax Calculation (top marginal 10.9%)" to job.audit_trail; set result.ny_military_retirement_exclusion = result.military_retirement_income; add "  NY IT-201 line 26 federal (military) pension subtraction: $" + result.ny_military_retirement_exclusion to job.audit_trail</t>
+    <t>set result.computed_state_tax = 0; set result.computed_state_taxable_income = 0; add "  New York Tax Calculation (top marginal 10.9%)" to job.audit_trail; set result.ny_military_retirement_exclusion = 0.0; if result.state_calc_resident_status is equal to "full_year" then { set result.ny_military_retirement_exclusion = result.military_retirement_income; } endif; add "  NY IT-201 line 26 federal (military) pension subtraction: $" + result.ny_military_retirement_exclusion to job.audit_trail</t>
   </si>
   <si>
     <t>CONDITIONS: COMMENTS</t>

--- a/sampleprojects/TaxReturn/excel/states/NY.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/NY.xlsx
@@ -44,7 +44,7 @@
     <t/>
   </si>
   <si>
-    <t>set result.computed_state_tax = 0; set result.computed_state_taxable_income = 0; add "  New York Tax Calculation (top marginal 10.9%)" to job.audit_trail</t>
+    <t>set result.computed_state_tax = 0; set result.computed_state_taxable_income = 0; add "  New York Tax Calculation (top marginal 10.9%)" to job.audit_trail; set result.ny_military_retirement_exclusion = 0.0; if result.state_calc_resident_status is equal to "full_year" then { set result.ny_military_retirement_exclusion = result.military_retirement_income; } endif; add "  NY IT-201 line 26 federal (military) pension subtraction: $" + result.ny_military_retirement_exclusion to job.audit_trail</t>
   </si>
   <si>
     <t>CONDITIONS: COMMENTS</t>
@@ -83,7 +83,7 @@
     <t>MFJ/QSS: $16,050 std ded, 10.9%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 16050.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.109</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.ny_military_retirement_exclusion - 16050.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.109</t>
   </si>
   <si>
     <t>X</t>
@@ -92,13 +92,13 @@
     <t>HOH: $11,200 std ded, 10.9%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 11200.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.109</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.ny_military_retirement_exclusion - 11200.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.109</t>
   </si>
   <si>
     <t>Default (Single/MFS): $8,000 std ded, 10.9%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 8000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.109</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.ny_military_retirement_exclusion - 8000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.109</t>
   </si>
   <si>
     <t>Policy:</t>
@@ -395,7 +395,7 @@
     <t>0.0</t>
   </si>
   <si>
-    <t>NY military retirement exclusion (computed - 100% exempt). New York Tax Law §612(c)(30). IT-201 Line 28 subtraction. New York provides full exclusion for US military retirement pay and SBP payments. No AGI limits. No age restrictions. One of most generous state military tax benefits. MOAA State Report Card 2025: Grade A. Honors MSRRA (spouse income exempt if different domicile) and SCRA (active duty pay exempt if different state of residence). Source: NYS Tax Department, MOAA</t>
+    <t>NY subtraction of military retired pay (computed per return in NY_Tax): pensions of the federal government, including the military, are subtracted in full on IT-201 line 26 (Tax Law 612(c)(3)(ii); 2025 IT-201-I p. 9). No age limit or cap; the $20,000 line 29 exclusion is for other pensions at 59 1/2 (#1330).</t>
   </si>
   <si>
     <t>ny_standard_deduction_hoh</t>
